--- a/Data/Hubs_Data_Actual_Reduced.xlsx
+++ b/Data/Hubs_Data_Actual_Reduced.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mottmac-my.sharepoint.com/personal/jonathan_field_mottmac_com/Documents/Documents/CCm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5AF9063-5778-486D-8270-B4E4E17B2D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{E5AF9063-5778-486D-8270-B4E4E17B2D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D4E5590-4805-4DEC-98CC-BBBDD1C8D487}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -415,6 +415,7 @@
     <col min="2" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -460,7 +461,7 @@
         <v>0.05</v>
       </c>
       <c r="G2">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -483,7 +484,7 @@
         <v>0.05</v>
       </c>
       <c r="G3">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -506,7 +507,7 @@
         <v>0.05</v>
       </c>
       <c r="G4">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -529,7 +530,7 @@
         <v>0.05</v>
       </c>
       <c r="G5">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -552,7 +553,7 @@
         <v>0.05</v>
       </c>
       <c r="G6">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -575,7 +576,7 @@
         <v>0.05</v>
       </c>
       <c r="G7">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -598,7 +599,7 @@
         <v>0.05</v>
       </c>
       <c r="G8">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -621,7 +622,7 @@
         <v>0.05</v>
       </c>
       <c r="G9">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -644,7 +645,7 @@
         <v>0.05</v>
       </c>
       <c r="G10">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -667,7 +668,7 @@
         <v>0.05</v>
       </c>
       <c r="G11">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -690,7 +691,7 @@
         <v>0.05</v>
       </c>
       <c r="G12">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -713,7 +714,7 @@
         <v>0.05</v>
       </c>
       <c r="G13">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -736,7 +737,7 @@
         <v>0.05</v>
       </c>
       <c r="G14">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -759,7 +760,7 @@
         <v>0.05</v>
       </c>
       <c r="G15">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -782,7 +783,7 @@
         <v>0.05</v>
       </c>
       <c r="G16">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -805,7 +806,7 @@
         <v>0.05</v>
       </c>
       <c r="G17">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -828,7 +829,7 @@
         <v>0.05</v>
       </c>
       <c r="G18">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -851,7 +852,7 @@
         <v>0.05</v>
       </c>
       <c r="G19">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -874,7 +875,7 @@
         <v>0.05</v>
       </c>
       <c r="G20">
-        <v>10000</v>
+        <v>150000</v>
       </c>
     </row>
   </sheetData>
